--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\urjita\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C20D8F4-5962-4442-9359-B6D2B805D73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7C35EF-A91F-4F0F-AFB3-EAAAA45EEEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -510,42 +510,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8370135A-FEA5-4137-A022-6996DCD692E5}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5435</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>SUM(A1:A3)</f>
         <v>5813</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H11">
-        <f>45*69</f>
-        <v>3105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H12">
-        <f>4589</f>
-        <v>4589</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -553,6 +541,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8B67BC-AC64-459C-9638-525D13C8A854}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="I14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
